--- a/manuscript_material/source_data/Source_Data_Fig5.xlsx
+++ b/manuscript_material/source_data/Source_Data_Fig5.xlsx
@@ -427,12 +427,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>configuration</t>
+          <t>model_configuration</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>galaxy_over_code_ratio</t>
+          <t>input_token_ratio</t>
         </is>
       </c>
     </row>
@@ -10783,17 +10783,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>execution_condition</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>configuration</t>
+          <t>model_configuration</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>input_token_ratio</t>
+          <t>input_token_usage_ratio_vs_gpt55</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -10808,7 +10808,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>acceptance_difference_pp</t>
+          <t>model_difference_accuracy_pp</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
@@ -10825,7 +10825,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -10855,7 +10855,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10885,7 +10885,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -10915,7 +10915,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -10945,7 +10945,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -10975,7 +10975,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -11005,7 +11005,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -11035,7 +11035,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -11096,7 +11096,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A version-dependent reference (bix-45-q1): current PhyKIT reproduces the Galaxy value; PhyKIT 2.0.3 the accepted value</t>
+          <t>A version-dependent reference (bix-45-q1): current PhyKIT reproduces the Galaxy value; PhyKIT 2.0.3 the value scored correct</t>
         </is>
       </c>
     </row>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>916 jobs ran with changed or dropped values; 3,436 more were blocked before submission</t>
+          <t>916 Galaxy jobs ran with parameter substitution; 3,436 more were blocked before submission</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Scoring route</t>
+          <t>Score conflict</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -11139,12 +11139,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Per-replicate trace</t>
+          <t>Replicate-run trace</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Why each rejected replicate diverged (45 open-ended code, 36 Galaxy)</t>
+          <t>Divergence mechanism of each scored-incorrect replicate run (45 open-ended code, 36 Galaxy)</t>
         </is>
       </c>
     </row>
@@ -11163,12 +11163,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Divergence source</t>
+          <t>Divergence mechanism</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>open-ended code 66.7%; Galaxy 13.9%</t>
+          <t>open-ended code condition 66.7%; Galaxy condition 13.9%</t>
         </is>
       </c>
     </row>
